--- a/data-manipulation-scripts/sheets-cleanup/sheets/VALVULA - 28_01 M.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/VALVULA - 28_01 M.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -43,22 +43,10 @@
     <t>VALVULA ADMISSAO WGK CB250F TWISTER 2016 EM DIANTE 10117491</t>
   </si>
   <si>
-    <t>7898558333786</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE WGK CBX250 TWISTER/ CB300/ XRE300 10111411</t>
-  </si>
-  <si>
     <t>7898924047231</t>
   </si>
   <si>
     <t>VALVULA ADMISSAO WGK BIZ110I/ POP110I 10117311</t>
-  </si>
-  <si>
-    <t>7899641818944</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE VEDAMOTORS FAN125 2009/ NXR125</t>
   </si>
   <si>
     <t>7895797890797</t>
@@ -67,22 +55,10 @@
     <t>VALVULA ADMISSAO VINI YS150 FAZER 2014/ XTZ150 2014 2020890079</t>
   </si>
   <si>
-    <t>7898558339948</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE WGK CB250F TWISTER 2016 EM DIANTE 10117501</t>
-  </si>
-  <si>
     <t>7899641863456</t>
   </si>
   <si>
     <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN FAN160 2015/ NX160 2016 210020</t>
-  </si>
-  <si>
-    <t>7899641810641</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE VEDAMOTORS TITAN CG FAN150 2009 210011</t>
   </si>
   <si>
     <t>7899641818937</t>
@@ -97,22 +73,10 @@
     <t>VALVULA ADMISSAO WGK YS150 FAZER 10114061</t>
   </si>
   <si>
-    <t>7898558336855</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE WGK YS150 FAZER 10114071</t>
-  </si>
-  <si>
     <t>7899641810658</t>
   </si>
   <si>
     <t>VALVULA ESCAPE VEDAMOTORS TITAN CG FAN150 2004 A 2008/ CRF150F 2012 210012</t>
-  </si>
-  <si>
-    <t>602883762640</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE IRON CBX250 TWISTER 185461</t>
   </si>
   <si>
     <t>602883762633</t>
@@ -127,34 +91,16 @@
     <t>VALVULA ADMISSAO IRON FAZER250 187691</t>
   </si>
   <si>
-    <t>7899641873400</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE VEDAMOTORS PCX150 2013 210024</t>
-  </si>
-  <si>
     <t>7895797890841</t>
   </si>
   <si>
     <t>VALVULA ESCAPE VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
   </si>
   <si>
-    <t>7895797890148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA ESCAPE VINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008 </t>
-  </si>
-  <si>
     <t>7899641879723</t>
   </si>
   <si>
     <t>VALVULA ADMISSAO VEDAMOTORS   PCX150 2013/ SH150I 2017 210024</t>
-  </si>
-  <si>
-    <t>7898558339580</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE WGK CG125 TODAY 1992 A 2001 10117091</t>
   </si>
   <si>
     <t>7898558339603</t>
@@ -175,18 +121,6 @@
     <t>VALVULA ADMISSAO VINI FACTOR YBR125 2000 A 2016/ XTZ125 2003 A 2015/ TTR125 2008 E.D</t>
   </si>
   <si>
-    <t>7895797890087</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
-  </si>
-  <si>
-    <t>7895797890186</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE VINI FACTOR YBR125 2000 A 2016/ XTZ125 2003 A 2015/ TTR125 2008 E.D</t>
-  </si>
-  <si>
     <t>7895797890124</t>
   </si>
   <si>
@@ -205,37 +139,22 @@
     <t>VALVULA ADMISSAOVINI FACTOR YBR125 2017 E.D</t>
   </si>
   <si>
-    <t>7893986549280</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE PECA+ BROS NXR150</t>
-  </si>
-  <si>
     <t>7895797890131</t>
   </si>
   <si>
     <t>VALVULA ADMISSAOVINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008</t>
   </si>
   <si>
-    <t>7895797890803</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPEVINI FAZER YS150 2014 E.D/ XTZ150 CROSSER E.D</t>
-  </si>
-  <si>
     <t>7895797890834</t>
   </si>
   <si>
-    <t>VALVULA ADMISSAOVINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
+    <t>VALVULA ADMISSAO VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
   </si>
   <si>
     <t>7895797890070</t>
   </si>
   <si>
     <t>VALVULA ADMISSAO VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE BIZ/ DREAM/ POP100cc 41018</t>
   </si>
   <si>
     <t>VALVULA ADMISSAO CG FAN ES/KS 41025</t>
@@ -256,24 +175,6 @@
     <t>VALVULA ADMISSAO MAHLE CG TITAN FAN125 2002 A 2004</t>
   </si>
   <si>
-    <t>0197892415557271304</t>
-  </si>
-  <si>
-    <t>VALVULA ADMISSAO MAHLE TITAN150cc 2004</t>
-  </si>
-  <si>
-    <t>0197894766665605304</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE MAHLE FAZER250cc GASOLINA</t>
-  </si>
-  <si>
-    <t>0197892415557394304</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE MAHLE TITAN150cc 2004</t>
-  </si>
-  <si>
     <t>0197892415478873304</t>
   </si>
   <si>
@@ -284,30 +185,6 @@
   </si>
   <si>
     <t>VALVULA ADMISSAO MAHLE CG125 INJECAO ELETRONICA</t>
-  </si>
-  <si>
-    <t>0197892415974092304</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE MAHLE CG125 INJECAO ELETRONICA</t>
-  </si>
-  <si>
-    <t>0197892415478644304</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
-  </si>
-  <si>
-    <t>0197892415557417304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA ESCAPE MAHLE YBR125cc </t>
-  </si>
-  <si>
-    <t>0197894766665520304</t>
-  </si>
-  <si>
-    <t>VALVULA ESCAPE MAHLE FAZER250cc FLEX</t>
   </si>
 </sst>
 </file>
@@ -647,7 +524,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -659,7 +536,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -671,7 +548,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="2">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -683,7 +560,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -695,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D9" s="3"/>
     </row>
@@ -707,7 +584,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -719,9 +596,11 @@
         <v>23</v>
       </c>
       <c r="C11" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -731,7 +610,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -743,9 +622,11 @@
         <v>27</v>
       </c>
       <c r="C13" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -755,9 +636,11 @@
         <v>29</v>
       </c>
       <c r="C14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -767,9 +650,11 @@
         <v>31</v>
       </c>
       <c r="C15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -779,10 +664,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D16" s="2">
-        <v>35.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="17">
@@ -793,136 +678,110 @@
         <v>35</v>
       </c>
       <c r="C17" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="2">
         <v>2.0</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D19" s="2">
-        <v>80.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="D19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="2">
-        <v>60.0</v>
-      </c>
+      <c r="D20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>60.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4"/>
+      <c r="B26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D25" s="2">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C26" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
@@ -931,34 +790,38 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C28" s="2">
         <v>1.0</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="2">
+        <v>70.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C29" s="2">
         <v>1.0</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="2">
+        <v>95.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
@@ -966,252 +829,124 @@
       <c r="D30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>65.0</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D35" s="2">
-        <v>60.0</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="4"/>
-      <c r="B37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2.0</v>
-      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="4"/>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="4"/>
-      <c r="B39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
       <c r="D40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D41" s="2">
-        <v>70.0</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="2">
-        <v>2.0</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
       <c r="D42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
       <c r="D43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D44" s="2">
-        <v>90.0</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>95.0</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D48" s="2">
-        <v>95.0</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D50" s="2">
-        <v>85.0</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="4"/>
@@ -6733,194 +6468,14 @@
       <c r="C970" s="3"/>
       <c r="D970" s="3"/>
     </row>
-    <row r="971">
-      <c r="A971" s="4"/>
-      <c r="B971" s="3"/>
-      <c r="C971" s="3"/>
-      <c r="D971" s="3"/>
-    </row>
-    <row r="972">
-      <c r="A972" s="4"/>
-      <c r="B972" s="3"/>
-      <c r="C972" s="3"/>
-      <c r="D972" s="3"/>
-    </row>
-    <row r="973">
-      <c r="A973" s="4"/>
-      <c r="B973" s="3"/>
-      <c r="C973" s="3"/>
-      <c r="D973" s="3"/>
-    </row>
-    <row r="974">
-      <c r="A974" s="4"/>
-      <c r="B974" s="3"/>
-      <c r="C974" s="3"/>
-      <c r="D974" s="3"/>
-    </row>
-    <row r="975">
-      <c r="A975" s="4"/>
-      <c r="B975" s="3"/>
-      <c r="C975" s="3"/>
-      <c r="D975" s="3"/>
-    </row>
-    <row r="976">
-      <c r="A976" s="4"/>
-      <c r="B976" s="3"/>
-      <c r="C976" s="3"/>
-      <c r="D976" s="3"/>
-    </row>
-    <row r="977">
-      <c r="A977" s="4"/>
-      <c r="B977" s="3"/>
-      <c r="C977" s="3"/>
-      <c r="D977" s="3"/>
-    </row>
-    <row r="978">
-      <c r="A978" s="4"/>
-      <c r="B978" s="3"/>
-      <c r="C978" s="3"/>
-      <c r="D978" s="3"/>
-    </row>
-    <row r="979">
-      <c r="A979" s="4"/>
-      <c r="B979" s="3"/>
-      <c r="C979" s="3"/>
-      <c r="D979" s="3"/>
-    </row>
-    <row r="980">
-      <c r="A980" s="4"/>
-      <c r="B980" s="3"/>
-      <c r="C980" s="3"/>
-      <c r="D980" s="3"/>
-    </row>
-    <row r="981">
-      <c r="A981" s="4"/>
-      <c r="B981" s="3"/>
-      <c r="C981" s="3"/>
-      <c r="D981" s="3"/>
-    </row>
-    <row r="982">
-      <c r="A982" s="4"/>
-      <c r="B982" s="3"/>
-      <c r="C982" s="3"/>
-      <c r="D982" s="3"/>
-    </row>
-    <row r="983">
-      <c r="A983" s="4"/>
-      <c r="B983" s="3"/>
-      <c r="C983" s="3"/>
-      <c r="D983" s="3"/>
-    </row>
-    <row r="984">
-      <c r="A984" s="4"/>
-      <c r="B984" s="3"/>
-      <c r="C984" s="3"/>
-      <c r="D984" s="3"/>
-    </row>
-    <row r="985">
-      <c r="A985" s="4"/>
-      <c r="B985" s="3"/>
-      <c r="C985" s="3"/>
-      <c r="D985" s="3"/>
-    </row>
-    <row r="986">
-      <c r="A986" s="4"/>
-      <c r="B986" s="3"/>
-      <c r="C986" s="3"/>
-      <c r="D986" s="3"/>
-    </row>
-    <row r="987">
-      <c r="A987" s="4"/>
-      <c r="B987" s="3"/>
-      <c r="C987" s="3"/>
-      <c r="D987" s="3"/>
-    </row>
-    <row r="988">
-      <c r="A988" s="4"/>
-      <c r="B988" s="3"/>
-      <c r="C988" s="3"/>
-      <c r="D988" s="3"/>
-    </row>
-    <row r="989">
-      <c r="A989" s="4"/>
-      <c r="B989" s="3"/>
-      <c r="C989" s="3"/>
-      <c r="D989" s="3"/>
-    </row>
-    <row r="990">
-      <c r="A990" s="4"/>
-      <c r="B990" s="3"/>
-      <c r="C990" s="3"/>
-      <c r="D990" s="3"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="4"/>
-      <c r="B991" s="3"/>
-      <c r="C991" s="3"/>
-      <c r="D991" s="3"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="4"/>
-      <c r="B992" s="3"/>
-      <c r="C992" s="3"/>
-      <c r="D992" s="3"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="4"/>
-      <c r="B993" s="3"/>
-      <c r="C993" s="3"/>
-      <c r="D993" s="3"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="4"/>
-      <c r="B994" s="3"/>
-      <c r="C994" s="3"/>
-      <c r="D994" s="3"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="4"/>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
-      <c r="D995" s="3"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="4"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A970">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A17 A19:A970">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
